--- a/exports/SHREECEM_full_report.xlsx
+++ b/exports/SHREECEM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:U64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.21</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>26040</v>
+        <v>25060.05</v>
       </c>
       <c r="I2" t="n">
         <v>26036.98436851406</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.2</v>
+        <v>-6.84</v>
       </c>
       <c r="L2" t="n">
-        <v>3.51</v>
+        <v>7.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.11</v>
+        <v>0.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>4.38</v>
       </c>
       <c r="O2" t="n">
         <v>-0.11</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.88</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>23491</v>
+        <v>24364</v>
       </c>
       <c r="I3" t="n">
         <v>23729.13131852682</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K3" t="n">
-        <v>6.26</v>
+        <v>2.78</v>
       </c>
       <c r="L3" t="n">
         <v>3.29</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.99</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>25150</v>
+        <v>24558</v>
       </c>
       <c r="I4" t="n">
         <v>24883.26246279414</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>3.23</v>
+        <v>0.8</v>
       </c>
       <c r="L4" t="n">
         <v>5.99</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="N4" t="n">
-        <v>3.72</v>
+        <v>4.96</v>
       </c>
       <c r="O4" t="n">
         <v>2.72</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.96</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44740.55208333334</v>
+        <v>44741.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>19350</v>
+        <v>19388</v>
       </c>
       <c r="I5" t="n">
         <v>19357.5338429777</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K5" t="n">
-        <v>21.21</v>
+        <v>21.05</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.15</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44824.55208333334</v>
+        <v>44825.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>23180.1</v>
+        <v>22291</v>
       </c>
       <c r="I6" t="n">
         <v>22992.46900853201</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>83.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K6" t="n">
-        <v>19.56</v>
+        <v>14.97</v>
       </c>
       <c r="L6" t="n">
         <v>2.67</v>
@@ -783,7 +854,7 @@
         <v>2.92</v>
       </c>
       <c r="N6" t="n">
-        <v>3.09</v>
+        <v>5.68</v>
       </c>
       <c r="O6" t="n">
         <v>0.26</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.36</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44854.38541666666</v>
+        <v>44854.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>21515</v>
+        <v>21940</v>
       </c>
       <c r="I7" t="n">
         <v>21690.13145253857</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>3.48</v>
+        <v>1.57</v>
       </c>
       <c r="L7" t="n">
         <v>5.01</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.41</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44914.55208333334</v>
+        <v>44915.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>23799.8</v>
+        <v>23478.75</v>
       </c>
       <c r="I8" t="n">
         <v>23581.84626458434</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>60</v>
+        <v>60.83333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>8.48</v>
+        <v>7.01</v>
       </c>
       <c r="L8" t="n">
         <v>4.96</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>4.7</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44944.55208333334</v>
+        <v>44945.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>24057.55</v>
+        <v>24435.45</v>
       </c>
       <c r="I9" t="n">
         <v>24320.97086619337</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.47</v>
+        <v>-4.07</v>
       </c>
       <c r="L9" t="n">
         <v>4.73</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>5.22</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44946.55208333334</v>
+        <v>44949.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>24308.35</v>
+        <v>23349</v>
       </c>
       <c r="I10" t="n">
         <v>23526.54540798818</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.52</v>
+        <v>-4.45</v>
       </c>
       <c r="L10" t="n">
-        <v>2.37</v>
+        <v>4.62</v>
       </c>
       <c r="M10" t="n">
         <v>0.24</v>
       </c>
       <c r="N10" t="n">
-        <v>0.17</v>
+        <v>5.02</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>8.06</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>22600</v>
+        <v>24409.1</v>
       </c>
       <c r="I11" t="n">
         <v>23305.30022591467</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.21</v>
+        <v>-4.54</v>
       </c>
       <c r="L11" t="n">
-        <v>5.14</v>
+        <v>5.66</v>
       </c>
       <c r="M11" t="n">
-        <v>0.62</v>
+        <v>5.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.03</v>
+        <v>5.58</v>
       </c>
       <c r="O11" t="n">
         <v>-5.02</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45002.55208333334</v>
+        <v>45005.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>25130</v>
+        <v>24838.65</v>
       </c>
       <c r="I12" t="n">
         <v>25089.77442768329</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K12" t="n">
-        <v>2.95</v>
+        <v>1.76</v>
       </c>
       <c r="L12" t="n">
         <v>6.79</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.46</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>25901</v>
+        <v>26389.95</v>
       </c>
       <c r="I13" t="n">
         <v>26258.24992899004</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.28</v>
+        <v>-6.25</v>
       </c>
       <c r="L13" t="n">
-        <v>4.72</v>
+        <v>6.39</v>
       </c>
       <c r="M13" t="n">
         <v>0.78</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>5.76</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45034.38541666666</v>
+        <v>45034.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>25420.75</v>
+        <v>25215.1</v>
       </c>
       <c r="I14" t="n">
         <v>25384.20869169446</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.67</v>
+        <v>-4.45</v>
       </c>
       <c r="L14" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="M14" t="n">
         <v>0.25</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.48</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45056.55208333334</v>
+        <v>45057.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>24470</v>
+        <v>24790</v>
       </c>
       <c r="I15" t="n">
         <v>24785.03224847707</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>2.95</v>
+        <v>1.69</v>
       </c>
       <c r="L15" t="n">
         <v>0.97</v>
@@ -1296,7 +1475,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="O15" t="n">
         <v>-1.31</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.33</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>25600</v>
+        <v>25160.05</v>
       </c>
       <c r="I16" t="n">
         <v>25348.3415947044</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K16" t="n">
-        <v>3.27</v>
+        <v>1.49</v>
       </c>
       <c r="L16" t="n">
         <v>4.37</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.51</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45133.38541666666</v>
+        <v>45133.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>24079.9</v>
+        <v>24235</v>
       </c>
       <c r="I17" t="n">
         <v>24112.67557628784</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>4.29</v>
+        <v>3.68</v>
       </c>
       <c r="L17" t="n">
         <v>1.95</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>4.68</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45156.38541666666</v>
+        <v>45156.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>23567.6</v>
+        <v>23545</v>
       </c>
       <c r="I18" t="n">
         <v>23555.59730688795</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.75</v>
+        <v>-2.85</v>
       </c>
       <c r="L18" t="n">
-        <v>3.01</v>
+        <v>3.23</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>3.45</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45170.55208333334</v>
+        <v>45173.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>24140</v>
+        <v>25250</v>
       </c>
       <c r="I19" t="n">
         <v>24356.43411795609</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.53</v>
+        <v>-7.24</v>
       </c>
       <c r="L19" t="n">
-        <v>3.31</v>
+        <v>7.37</v>
       </c>
       <c r="M19" t="n">
-        <v>0.53</v>
+        <v>1.86</v>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>6.13</v>
       </c>
       <c r="O19" t="n">
         <v>-1.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.45</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45197.38541666666</v>
+        <v>45197.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>26022.1</v>
+        <v>25633.65</v>
       </c>
       <c r="I20" t="n">
         <v>25771.62628894218</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>3.06</v>
+        <v>1.52</v>
       </c>
       <c r="L20" t="n">
         <v>3.17</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>4.75</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>26221.95</v>
+        <v>26529.95</v>
       </c>
       <c r="I21" t="n">
         <v>26379.60053915119</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.3</v>
+        <v>-3.5</v>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>5.02</v>
       </c>
       <c r="M21" t="n">
         <v>0.65</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>3.75</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>26125</v>
+        <v>25821.55</v>
       </c>
       <c r="I22" t="n">
         <v>25987.43662814466</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.53</v>
+        <v>-2.67</v>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>2.74</v>
       </c>
       <c r="M22" t="n">
         <v>0.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="O22" t="n">
         <v>1.33</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>4.98</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45237.38541666666</v>
+        <v>45237.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>26536.1</v>
+        <v>26613.25</v>
       </c>
       <c r="I23" t="n">
         <v>26574.92061597797</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.77</v>
+        <v>-3.07</v>
       </c>
       <c r="L23" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
         <v>0.96</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>3.89</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45295.55208333334</v>
+        <v>45296.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>28340.05</v>
+        <v>27127.95</v>
       </c>
       <c r="I24" t="n">
         <v>27752.79757754115</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>58</v>
+        <v>58.83333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>6.49</v>
+        <v>1.93</v>
       </c>
       <c r="L24" t="n">
         <v>3.81</v>
@@ -1809,7 +2096,7 @@
         <v>0.54</v>
       </c>
       <c r="N24" t="n">
-        <v>1.52</v>
+        <v>4.83</v>
       </c>
       <c r="O24" t="n">
         <v>0.85</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.89</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45310.55208333334</v>
+        <v>45311.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>26651</v>
+        <v>27445</v>
       </c>
       <c r="I25" t="n">
         <v>27240.56771884825</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.76</v>
+        <v>-1.17</v>
       </c>
       <c r="L25" t="n">
         <v>4.14</v>
@@ -1866,7 +2165,7 @@
         <v>0.87</v>
       </c>
       <c r="N25" t="n">
-        <v>1.52</v>
+        <v>2.93</v>
       </c>
       <c r="O25" t="n">
         <v>-4.83</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.1</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45324.55208333334</v>
+        <v>45327.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>28450</v>
+        <v>27527.1</v>
       </c>
       <c r="I26" t="n">
         <v>27843.39425206587</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K26" t="n">
-        <v>3.66</v>
+        <v>0.3</v>
       </c>
       <c r="L26" t="n">
         <v>3.23</v>
@@ -1923,7 +2234,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>5.27</v>
       </c>
       <c r="O26" t="n">
         <v>2.93</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>11.17</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>25600</v>
+        <v>25917.1</v>
       </c>
       <c r="I27" t="n">
         <v>25829.64419211044</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K27" t="n">
-        <v>7</v>
+        <v>5.85</v>
       </c>
       <c r="L27" t="n">
         <v>5.35</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>4.13</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>25418.95</v>
+        <v>25298</v>
       </c>
       <c r="I28" t="n">
         <v>25341.45332728417</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.92</v>
+        <v>-2.39</v>
       </c>
       <c r="L28" t="n">
-        <v>2.76</v>
+        <v>3.53</v>
       </c>
       <c r="M28" t="n">
         <v>0.65</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>4.41</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45414.55208333334</v>
+        <v>45415.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>24817</v>
+        <v>25756.55</v>
       </c>
       <c r="I29" t="n">
         <v>25002.77037554946</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K29" t="n">
-        <v>1.9</v>
+        <v>-1.81</v>
       </c>
       <c r="L29" t="n">
-        <v>0.91</v>
+        <v>2.36</v>
       </c>
       <c r="M29" t="n">
         <v>0.87</v>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>3.68</v>
       </c>
       <c r="O29" t="n">
         <v>-0.14</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>6.86</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45443.38541666666</v>
+        <v>45443.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>25000</v>
+        <v>24638.4</v>
       </c>
       <c r="I30" t="n">
         <v>24838.88551133942</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.94</v>
+        <v>-4.34</v>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>4.47</v>
       </c>
       <c r="M30" t="n">
         <v>0.62</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>5.32</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>25546</v>
+        <v>26032.15</v>
       </c>
       <c r="I31" t="n">
         <v>25950.18475319313</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.68</v>
+        <v>-5.66</v>
       </c>
       <c r="L31" t="n">
-        <v>4.71</v>
+        <v>6.02</v>
       </c>
       <c r="M31" t="n">
         <v>2.28</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.67</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>27198</v>
+        <v>26572.3</v>
       </c>
       <c r="I32" t="n">
         <v>26871.58656362952</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K32" t="n">
-        <v>4.48</v>
+        <v>2.07</v>
       </c>
       <c r="L32" t="n">
         <v>2</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>5.79</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45534.38541666666</v>
+        <v>45534.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>25400</v>
+        <v>25531</v>
       </c>
       <c r="I33" t="n">
         <v>25423.79512248118</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>4.41</v>
+        <v>3.92</v>
       </c>
       <c r="L33" t="n">
         <v>1.96</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>3.74</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45552.55208333334</v>
+        <v>45553.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>25417.95</v>
+        <v>25040</v>
       </c>
       <c r="I34" t="n">
         <v>25118.63240509524</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.44</v>
+        <v>-1.92</v>
       </c>
       <c r="L34" t="n">
-        <v>1.06</v>
+        <v>2.04</v>
       </c>
       <c r="M34" t="n">
         <v>0.78</v>
       </c>
       <c r="N34" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="O34" t="n">
         <v>2.81</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>4.4</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45558.38541666666</v>
+        <v>45558.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>25679.9</v>
+        <v>25882.6</v>
       </c>
       <c r="I35" t="n">
         <v>25805.95099474486</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.56</v>
+        <v>-3.37</v>
       </c>
       <c r="L35" t="n">
-        <v>2.59</v>
+        <v>4.22</v>
       </c>
       <c r="M35" t="n">
         <v>0.4</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>4.49</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45572.38541666666</v>
+        <v>45572.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>25666.85</v>
+        <v>25295</v>
       </c>
       <c r="I36" t="n">
         <v>25408.96288236215</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.83</v>
+        <v>-2.27</v>
       </c>
       <c r="L36" t="n">
-        <v>1.18</v>
+        <v>2.48</v>
       </c>
       <c r="M36" t="n">
         <v>0.54</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.47</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45588.55208333334</v>
+        <v>45589.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>24700</v>
+        <v>25242.45</v>
       </c>
       <c r="I37" t="n">
         <v>25117.9960568082</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>2.35</v>
+        <v>0.21</v>
       </c>
       <c r="L37" t="n">
         <v>1.47</v>
@@ -2550,7 +2993,7 @@
         <v>0.6</v>
       </c>
       <c r="N37" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="O37" t="n">
         <v>-2.45</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>5.44</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>24525.05</v>
+        <v>24330</v>
       </c>
       <c r="I38" t="n">
         <v>24399.28809290272</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.84</v>
+        <v>-3.61</v>
       </c>
       <c r="L38" t="n">
-        <v>3.95</v>
+        <v>4.41</v>
       </c>
       <c r="M38" t="n">
         <v>0.72</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>4.13</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>24814</v>
+        <v>25436.5</v>
       </c>
       <c r="I39" t="n">
         <v>25050.35582835157</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.99</v>
+        <v>-4.55</v>
       </c>
       <c r="L39" t="n">
-        <v>2.02</v>
+        <v>5.89</v>
       </c>
       <c r="M39" t="n">
-        <v>0.19</v>
+        <v>0.64</v>
       </c>
       <c r="N39" t="n">
-        <v>2.78</v>
+        <v>3.17</v>
       </c>
       <c r="O39" t="n">
         <v>-0.41</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.53</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>27234.75</v>
+        <v>27041.15</v>
       </c>
       <c r="I40" t="n">
         <v>27179.32568469519</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>7.07</v>
+        <v>6.31</v>
       </c>
       <c r="L40" t="n">
         <v>2.49</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.58</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45685.55208333334</v>
+        <v>45686.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>26044.5</v>
+        <v>26831.7</v>
       </c>
       <c r="I41" t="n">
         <v>26167.59539432669</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>39</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>3.69</v>
+        <v>0.77</v>
       </c>
       <c r="L41" t="n">
         <v>1.27</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.73</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45715.55208333334</v>
+        <v>45716.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>28210</v>
+        <v>27275.55</v>
       </c>
       <c r="I42" t="n">
         <v>27365.2826148821</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>5.14</v>
+        <v>1.65</v>
       </c>
       <c r="L42" t="n">
         <v>3.49</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.57</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45736.38541666666</v>
+        <v>45736.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>28394.75</v>
+        <v>28744</v>
       </c>
       <c r="I43" t="n">
         <v>28666.67525355081</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.1</v>
+        <v>-5.38</v>
       </c>
       <c r="L43" t="n">
         <v>5.59</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>5.38</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>29740</v>
+        <v>29085</v>
       </c>
       <c r="I44" t="n">
         <v>29676.35134317077</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>41</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K44" t="n">
-        <v>3.47</v>
+        <v>1.19</v>
       </c>
       <c r="L44" t="n">
         <v>1.42</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.82</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45790.55208333334</v>
+        <v>45791.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>30010</v>
+        <v>30785</v>
       </c>
       <c r="I45" t="n">
         <v>30643.13859327913</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.18</v>
+        <v>-5.84</v>
       </c>
       <c r="L45" t="n">
-        <v>4.68</v>
+        <v>5.97</v>
       </c>
       <c r="M45" t="n">
         <v>1.4</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>6.46</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45804.55208333334</v>
+        <v>45805.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>31100</v>
+        <v>30115</v>
       </c>
       <c r="I46" t="n">
         <v>30340.37444476527</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K46" t="n">
-        <v>1.02</v>
+        <v>-2.18</v>
       </c>
       <c r="L46" t="n">
-        <v>2.19</v>
+        <v>2.79</v>
       </c>
       <c r="M46" t="n">
         <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="O46" t="n">
         <v>2.68</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.65</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45833.55208333334</v>
+        <v>45834.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>29185</v>
+        <v>30015</v>
       </c>
       <c r="I47" t="n">
         <v>29565.50282318233</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K47" t="n">
-        <v>3.09</v>
+        <v>0.33</v>
       </c>
       <c r="L47" t="n">
         <v>3.7</v>
@@ -3120,7 +3683,7 @@
         <v>1.11</v>
       </c>
       <c r="N47" t="n">
-        <v>2.53</v>
+        <v>3.22</v>
       </c>
       <c r="O47" t="n">
         <v>-3.86</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.53</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>31670</v>
+        <v>31020</v>
       </c>
       <c r="I48" t="n">
         <v>31112.6954568271</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K48" t="n">
-        <v>5.51</v>
+        <v>3.35</v>
       </c>
       <c r="L48" t="n">
         <v>2.95</v>
@@ -3177,7 +3752,7 @@
         <v>0.4</v>
       </c>
       <c r="N48" t="n">
-        <v>1.48</v>
+        <v>2.26</v>
       </c>
       <c r="O48" t="n">
         <v>3.22</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5.5</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>30450</v>
+        <v>31625</v>
       </c>
       <c r="I49" t="n">
         <v>31528.05154312756</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>1.84</v>
+        <v>-1.95</v>
       </c>
       <c r="L49" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="M49" t="n">
-        <v>1.08</v>
+        <v>1.81</v>
       </c>
       <c r="N49" t="n">
-        <v>0.76</v>
+        <v>2.96</v>
       </c>
       <c r="O49" t="n">
         <v>-2.26</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.53</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45891.38541666666</v>
+        <v>45891.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>30100</v>
+        <v>30000</v>
       </c>
       <c r="I50" t="n">
         <v>30057.32825006668</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.82</v>
+        <v>-5.14</v>
       </c>
       <c r="L50" t="n">
         <v>5.42</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.83</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>29885</v>
+        <v>30175</v>
       </c>
       <c r="I51" t="n">
         <v>30131.56704584859</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>54</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>0.38</v>
+        <v>-0.58</v>
       </c>
       <c r="L51" t="n">
         <v>2.5</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>3.38</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45947.55208333334</v>
+        <v>45950.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>29650</v>
+        <v>28955</v>
       </c>
       <c r="I52" t="n">
         <v>29165.67241313511</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.74</v>
+        <v>-4.04</v>
       </c>
       <c r="L52" t="n">
-        <v>2.07</v>
+        <v>4.67</v>
       </c>
       <c r="M52" t="n">
         <v>-0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.97</v>
+        <v>2.63</v>
       </c>
       <c r="O52" t="n">
         <v>0.18</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>5.31</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46022.38541666666</v>
+        <v>46022.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>26405</v>
+        <v>26635</v>
       </c>
       <c r="I53" t="n">
         <v>26469.10315840518</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>72</v>
+        <v>72.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>8.81</v>
+        <v>8.01</v>
       </c>
       <c r="L53" t="n">
         <v>3.06</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>3.26</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46052.55208333334</v>
+        <v>46054.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>26955</v>
+        <v>26620</v>
       </c>
       <c r="I54" t="n">
         <v>26891.67552263039</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>30</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>1.2</v>
+        <v>-0.06</v>
       </c>
       <c r="L54" t="n">
-        <v>0.88</v>
+        <v>1.16</v>
       </c>
       <c r="M54" t="n">
         <v>0.68</v>
       </c>
       <c r="N54" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="O54" t="n">
         <v>0.89</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.41</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>23385</v>
+        <v>24135</v>
       </c>
       <c r="I55" t="n">
         <v>23950.63984147458</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K55" t="n">
-        <v>12.15</v>
+        <v>9.34</v>
       </c>
       <c r="L55" t="n">
         <v>3.47</v>
@@ -3576,7 +4235,7 @@
         <v>1.64</v>
       </c>
       <c r="N55" t="n">
-        <v>2.79</v>
+        <v>3.74</v>
       </c>
       <c r="O55" t="n">
         <v>-1.87</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.99</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>24615</v>
+        <v>24140</v>
       </c>
       <c r="I56" t="n">
         <v>24507.77010833146</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K56" t="n">
-        <v>1.99</v>
+        <v>0.02</v>
       </c>
       <c r="L56" t="n">
         <v>6.05</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.78</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>25060</v>
+        <v>25895</v>
       </c>
       <c r="I57" t="n">
         <v>25520.2418090194</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.81</v>
+        <v>-7.27</v>
       </c>
       <c r="L57" t="n">
-        <v>4.39</v>
+        <v>7.66</v>
       </c>
       <c r="M57" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="N57" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="O57" t="n">
         <v>-1.32</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.47</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46177.55208333334</v>
+        <v>46178.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>24495</v>
+        <v>24080</v>
       </c>
       <c r="I58" t="n">
         <v>24307.72436842306</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.41</v>
+        <v>-7.01</v>
       </c>
       <c r="L58" t="n">
         <v>7.36</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.05</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>24170</v>
+        <v>24925</v>
       </c>
       <c r="I59" t="n">
         <v>24418.67287298234</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.37</v>
+        <v>-3.51</v>
       </c>
       <c r="L59" t="n">
-        <v>2.53</v>
+        <v>4.36</v>
       </c>
       <c r="M59" t="n">
-        <v>0.53</v>
+        <v>2.09</v>
       </c>
       <c r="N59" t="n">
-        <v>1.81</v>
+        <v>2.71</v>
       </c>
       <c r="O59" t="n">
         <v>-1.57</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.61</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46244.55208333334</v>
+        <v>46245.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>26025</v>
+        <v>25530</v>
       </c>
       <c r="I60" t="n">
         <v>25972.74328506285</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K60" t="n">
-        <v>4.41</v>
+        <v>2.43</v>
       </c>
       <c r="L60" t="n">
         <v>1.5</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.04</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>24495</v>
+        <v>24955</v>
       </c>
       <c r="I61" t="n">
         <v>24911.42742318402</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>4.05</v>
+        <v>2.25</v>
       </c>
       <c r="L61" t="n">
         <v>2.37</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>4.48</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>23940</v>
+        <v>23815</v>
       </c>
       <c r="I62" t="n">
         <v>23925.45671764897</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.07</v>
+        <v>-4.57</v>
       </c>
       <c r="L62" t="n">
-        <v>4.23</v>
+        <v>4.99</v>
       </c>
       <c r="M62" t="n">
         <v>-0</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.26</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46318.38541666666</v>
+        <v>46318.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>22505</v>
+        <v>22750</v>
       </c>
       <c r="I63" t="n">
         <v>22634.39990780714</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K63" t="n">
-        <v>5.5</v>
+        <v>4.47</v>
       </c>
       <c r="L63" t="n">
         <v>1.36</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4092,6 +4859,14 @@
       <c r="Q64" t="n">
         <v>7</v>
       </c>
+      <c r="R64" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6194,7 +6969,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="6">
@@ -6204,7 +6979,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="7">
@@ -6214,7 +6989,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -6224,7 +6999,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6234,7 +7009,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="10">
@@ -6244,7 +7019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -6254,7 +7029,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -6264,7 +7039,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6274,7 +7049,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.40000000000001</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="14">
@@ -6284,7 +7059,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.82</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="15">
@@ -6294,7 +7069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.56</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="16">
@@ -6304,7 +7079,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.07</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="17">
@@ -6314,7 +7089,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21.21</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="18">
@@ -6324,7 +7099,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.1</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="19">
@@ -6334,7 +7109,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.27</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="20">
@@ -6344,7 +7119,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.12</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="21">
@@ -6354,7 +7129,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.36</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="22">
@@ -6364,7 +7139,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -6384,7 +7159,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="25">
@@ -6394,7 +7169,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.82</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="26">
@@ -6404,7 +7179,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.41</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="27">
@@ -6414,7 +7189,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.63</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="28">
@@ -6424,7 +7199,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
